--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124665953</v>
       </c>
       <c r="B2" t="n">
-        <v>98123</v>
+        <v>98291</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -680,11 +680,6 @@
       <c r="B2" t="n">
         <v>98291</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>LC</t>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,2297 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128985878</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92816</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>720769</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6626378</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128985894</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>720563</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6626412</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128985884</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98658</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>720568</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6626387</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128985897</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>720543</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6626360</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128985886</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92443</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>720581</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6626397</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128985900</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92443</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>720544</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6626397</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128985888</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>720578</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6626426</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128985887</v>
+      </c>
+      <c r="B10" t="n">
+        <v>105686</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>720586</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6626407</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128985901</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92443</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>720521</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6626398</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128985898</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91281</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>720530</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6626369</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128985907</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100824</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>720516</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6626359</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128985893</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58579</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>720574</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6626394</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128985908</v>
+      </c>
+      <c r="B15" t="n">
+        <v>86939</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>720504</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6626377</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128985876</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92443</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>720766</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6626378</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128985879</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>720754</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6626384</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128985885</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>720573</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6626380</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128985895</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>720572</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6626395</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128985882</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91877</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>720643</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6626413</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128985873</v>
+      </c>
+      <c r="B21" t="n">
+        <v>86855</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>445</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kopparspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius cupreorufus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>720771</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6626378</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128985896</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>720577</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6626370</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128985902</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92443</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>720521</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6626387</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128985875</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92834</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>720769</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6626395</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128985899</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58577</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>720542</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6626391</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -781,45 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B3" t="n">
-        <v>92816</v>
+        <v>92834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R3" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,6 +863,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -878,48 +882,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B4" t="n">
-        <v>92834</v>
+        <v>92816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R4" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -960,7 +961,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B5" t="n">
-        <v>98658</v>
+        <v>92834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,34 +990,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R5" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1058,6 +1061,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1076,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985897</v>
+        <v>128985884</v>
       </c>
       <c r="B6" t="n">
-        <v>92834</v>
+        <v>98658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,37 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720543</v>
+        <v>720568</v>
       </c>
       <c r="R6" t="n">
-        <v>6626360</v>
+        <v>6626387</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1158,7 +1159,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985886</v>
+        <v>128985888</v>
       </c>
       <c r="B7" t="n">
-        <v>92443</v>
+        <v>92834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,34 +1188,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720581</v>
+        <v>720578</v>
       </c>
       <c r="R7" t="n">
-        <v>6626397</v>
+        <v>6626426</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1256,6 +1259,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1371,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985888</v>
+        <v>128985886</v>
       </c>
       <c r="B9" t="n">
-        <v>92834</v>
+        <v>92443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1382,37 +1386,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720578</v>
+        <v>720581</v>
       </c>
       <c r="R9" t="n">
-        <v>6626426</v>
+        <v>6626397</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1453,7 +1454,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985908</v>
+        <v>128985876</v>
       </c>
       <c r="B15" t="n">
-        <v>86939</v>
+        <v>92443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720504</v>
+        <v>720766</v>
       </c>
       <c r="R15" t="n">
-        <v>6626377</v>
+        <v>6626378</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985876</v>
+        <v>128985908</v>
       </c>
       <c r="B16" t="n">
-        <v>92443</v>
+        <v>86939</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2065,21 +2065,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>1988</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720766</v>
+        <v>720504</v>
       </c>
       <c r="R16" t="n">
-        <v>6626378</v>
+        <v>6626377</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2454,32 +2454,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985882</v>
+        <v>128985896</v>
       </c>
       <c r="B20" t="n">
-        <v>91877</v>
+        <v>92834</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1506</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720643</v>
+        <v>720577</v>
       </c>
       <c r="R20" t="n">
-        <v>6626413</v>
+        <v>6626370</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2530,39 +2530,15 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2579,45 +2555,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985873</v>
+        <v>128985875</v>
       </c>
       <c r="B21" t="n">
-        <v>86855</v>
+        <v>92834</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720771</v>
+        <v>720769</v>
       </c>
       <c r="R21" t="n">
-        <v>6626378</v>
+        <v>6626395</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2658,6 +2637,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2676,10 +2656,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B22" t="n">
-        <v>92834</v>
+        <v>92443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2687,37 +2667,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R22" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2758,7 +2735,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2777,10 +2753,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985902</v>
+        <v>128985899</v>
       </c>
       <c r="B23" t="n">
-        <v>92443</v>
+        <v>58577</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,21 +2764,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4769</v>
+        <v>208250</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2812,10 +2788,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720521</v>
+        <v>720542</v>
       </c>
       <c r="R23" t="n">
-        <v>6626387</v>
+        <v>6626391</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2874,48 +2850,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985875</v>
+        <v>128985873</v>
       </c>
       <c r="B24" t="n">
-        <v>92834</v>
+        <v>86855</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>445</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720769</v>
+        <v>720771</v>
       </c>
       <c r="R24" t="n">
-        <v>6626395</v>
+        <v>6626378</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2956,7 +2929,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2975,45 +2947,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985899</v>
+        <v>128985882</v>
       </c>
       <c r="B25" t="n">
-        <v>58577</v>
+        <v>91877</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208250</v>
+        <v>1506</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720542</v>
+        <v>720643</v>
       </c>
       <c r="R25" t="n">
-        <v>6626391</v>
+        <v>6626413</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3048,6 +3023,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3056,6 +3036,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -781,48 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B3" t="n">
-        <v>92834</v>
+        <v>92821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R3" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,7 +860,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,45 +878,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B4" t="n">
-        <v>92816</v>
+        <v>92839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R4" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -961,6 +960,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,7 +982,7 @@
         <v>128985897</v>
       </c>
       <c r="B5" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>128985884</v>
       </c>
       <c r="B6" t="n">
-        <v>98658</v>
+        <v>98665</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985888</v>
+        <v>128985900</v>
       </c>
       <c r="B7" t="n">
-        <v>92834</v>
+        <v>92448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,37 +1188,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720578</v>
+        <v>720544</v>
       </c>
       <c r="R7" t="n">
-        <v>6626426</v>
+        <v>6626397</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1259,7 +1256,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1278,10 +1274,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985900</v>
+        <v>128985886</v>
       </c>
       <c r="B8" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,7 +1309,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720544</v>
+        <v>720581</v>
       </c>
       <c r="R8" t="n">
         <v>6626397</v>
@@ -1375,10 +1371,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985886</v>
+        <v>128985888</v>
       </c>
       <c r="B9" t="n">
-        <v>92443</v>
+        <v>92839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,34 +1382,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720581</v>
+        <v>720578</v>
       </c>
       <c r="R9" t="n">
-        <v>6626397</v>
+        <v>6626426</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1454,6 +1453,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>128985887</v>
       </c>
       <c r="B10" t="n">
-        <v>105686</v>
+        <v>105693</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>128985901</v>
       </c>
       <c r="B11" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128985898</v>
       </c>
       <c r="B12" t="n">
-        <v>91281</v>
+        <v>91286</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128985907</v>
       </c>
       <c r="B13" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>128985893</v>
       </c>
       <c r="B14" t="n">
-        <v>58579</v>
+        <v>58582</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985876</v>
+        <v>128985908</v>
       </c>
       <c r="B15" t="n">
-        <v>92443</v>
+        <v>86944</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>1988</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720766</v>
+        <v>720504</v>
       </c>
       <c r="R15" t="n">
-        <v>6626378</v>
+        <v>6626377</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985908</v>
+        <v>128985879</v>
       </c>
       <c r="B16" t="n">
-        <v>86939</v>
+        <v>92839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2065,34 +2065,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1988</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720504</v>
+        <v>720754</v>
       </c>
       <c r="R16" t="n">
-        <v>6626377</v>
+        <v>6626384</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2133,6 +2136,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2151,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985879</v>
+        <v>128985876</v>
       </c>
       <c r="B17" t="n">
-        <v>92834</v>
+        <v>92448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2162,37 +2166,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720754</v>
+        <v>720766</v>
       </c>
       <c r="R17" t="n">
-        <v>6626384</v>
+        <v>6626378</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2233,7 +2234,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>128985885</v>
       </c>
       <c r="B18" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128985895</v>
       </c>
       <c r="B19" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,10 +2454,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B20" t="n">
-        <v>92834</v>
+        <v>92448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2465,37 +2465,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R20" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2536,7 +2533,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2555,10 +2551,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B21" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,10 +2589,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R21" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2656,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985902</v>
+        <v>128985875</v>
       </c>
       <c r="B22" t="n">
-        <v>92443</v>
+        <v>92839</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2667,34 +2663,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720521</v>
+        <v>720769</v>
       </c>
       <c r="R22" t="n">
-        <v>6626387</v>
+        <v>6626395</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2735,6 +2734,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2753,32 +2753,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985899</v>
+        <v>128985873</v>
       </c>
       <c r="B23" t="n">
-        <v>58577</v>
+        <v>86860</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>208250</v>
+        <v>445</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720542</v>
+        <v>720771</v>
       </c>
       <c r="R23" t="n">
-        <v>6626391</v>
+        <v>6626378</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985873</v>
+        <v>128985882</v>
       </c>
       <c r="B24" t="n">
-        <v>86855</v>
+        <v>91882</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2861,34 +2861,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>445</v>
+        <v>1506</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720771</v>
+        <v>720643</v>
       </c>
       <c r="R24" t="n">
-        <v>6626378</v>
+        <v>6626413</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2923,6 +2926,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -2931,6 +2939,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -2947,48 +2975,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985882</v>
+        <v>128985899</v>
       </c>
       <c r="B25" t="n">
-        <v>91877</v>
+        <v>58580</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1506</v>
+        <v>208250</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720643</v>
+        <v>720542</v>
       </c>
       <c r="R25" t="n">
-        <v>6626413</v>
+        <v>6626391</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3023,11 +3048,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3036,26 +3056,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -781,45 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B3" t="n">
-        <v>92829</v>
+        <v>92847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R3" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,6 +863,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -878,48 +882,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B4" t="n">
-        <v>92847</v>
+        <v>92829</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R4" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -960,7 +961,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985908</v>
+        <v>128985876</v>
       </c>
       <c r="B15" t="n">
-        <v>86951</v>
+        <v>92456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720504</v>
+        <v>720766</v>
       </c>
       <c r="R15" t="n">
-        <v>6626377</v>
+        <v>6626378</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985876</v>
+        <v>128985879</v>
       </c>
       <c r="B16" t="n">
-        <v>92456</v>
+        <v>92847</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2065,34 +2065,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720766</v>
+        <v>720754</v>
       </c>
       <c r="R16" t="n">
-        <v>6626378</v>
+        <v>6626384</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2133,6 +2136,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2151,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985879</v>
+        <v>128985908</v>
       </c>
       <c r="B17" t="n">
-        <v>92847</v>
+        <v>86951</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2162,37 +2166,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720754</v>
+        <v>720504</v>
       </c>
       <c r="R17" t="n">
-        <v>6626384</v>
+        <v>6626377</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2233,7 +2234,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2454,45 +2454,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985902</v>
+        <v>128985882</v>
       </c>
       <c r="B20" t="n">
-        <v>92456</v>
+        <v>91890</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>1506</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720521</v>
+        <v>720643</v>
       </c>
       <c r="R20" t="n">
-        <v>6626387</v>
+        <v>6626413</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2527,6 +2530,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2535,6 +2543,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2648,48 +2676,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985882</v>
+        <v>128985902</v>
       </c>
       <c r="B22" t="n">
-        <v>91890</v>
+        <v>92456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1506</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720643</v>
+        <v>720521</v>
       </c>
       <c r="R22" t="n">
-        <v>6626413</v>
+        <v>6626387</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2724,11 +2749,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2737,26 +2757,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -781,48 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B3" t="n">
-        <v>92847</v>
+        <v>92834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R3" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,7 +860,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,45 +878,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B4" t="n">
-        <v>92829</v>
+        <v>92852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R4" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -961,6 +960,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B5" t="n">
-        <v>98673</v>
+        <v>92852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,34 +990,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R5" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1058,6 +1061,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1076,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985897</v>
+        <v>128985884</v>
       </c>
       <c r="B6" t="n">
-        <v>92847</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,37 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720543</v>
+        <v>720568</v>
       </c>
       <c r="R6" t="n">
-        <v>6626360</v>
+        <v>6626387</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1158,7 +1159,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985886</v>
+        <v>128985900</v>
       </c>
       <c r="B7" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720581</v>
+        <v>720544</v>
       </c>
       <c r="R7" t="n">
         <v>6626397</v>
@@ -1274,10 +1274,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985900</v>
+        <v>128985886</v>
       </c>
       <c r="B8" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720544</v>
+        <v>720581</v>
       </c>
       <c r="R8" t="n">
         <v>6626397</v>
@@ -1374,7 +1374,7 @@
         <v>128985888</v>
       </c>
       <c r="B9" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>128985887</v>
       </c>
       <c r="B10" t="n">
-        <v>105701</v>
+        <v>105706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>128985901</v>
       </c>
       <c r="B11" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128985898</v>
       </c>
       <c r="B12" t="n">
-        <v>91293</v>
+        <v>91296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128985907</v>
       </c>
       <c r="B13" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985876</v>
+        <v>128985879</v>
       </c>
       <c r="B15" t="n">
-        <v>92456</v>
+        <v>92852</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1968,34 +1968,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720766</v>
+        <v>720754</v>
       </c>
       <c r="R15" t="n">
-        <v>6626378</v>
+        <v>6626384</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2036,6 +2039,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2054,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985879</v>
+        <v>128985876</v>
       </c>
       <c r="B16" t="n">
-        <v>92847</v>
+        <v>92461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2065,37 +2069,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720754</v>
+        <v>720766</v>
       </c>
       <c r="R16" t="n">
-        <v>6626384</v>
+        <v>6626378</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2136,7 +2137,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>128985908</v>
       </c>
       <c r="B17" t="n">
-        <v>86951</v>
+        <v>86954</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>128985885</v>
       </c>
       <c r="B18" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128985895</v>
       </c>
       <c r="B19" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,32 +2454,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985882</v>
+        <v>128985875</v>
       </c>
       <c r="B20" t="n">
-        <v>91890</v>
+        <v>92852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1506</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720643</v>
+        <v>720769</v>
       </c>
       <c r="R20" t="n">
-        <v>6626413</v>
+        <v>6626395</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2530,39 +2530,15 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2582,7 +2558,7 @@
         <v>128985873</v>
       </c>
       <c r="B21" t="n">
-        <v>86867</v>
+        <v>86870</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,7 +2655,7 @@
         <v>128985902</v>
       </c>
       <c r="B22" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2773,32 +2749,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985896</v>
+        <v>128985882</v>
       </c>
       <c r="B23" t="n">
-        <v>92847</v>
+        <v>91893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>1506</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2811,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720577</v>
+        <v>720643</v>
       </c>
       <c r="R23" t="n">
-        <v>6626370</v>
+        <v>6626413</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2849,15 +2825,39 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2874,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B24" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R24" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -781,45 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B3" t="n">
-        <v>92834</v>
+        <v>92855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R3" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,6 +863,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -878,48 +882,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B4" t="n">
-        <v>92852</v>
+        <v>92837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R4" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -960,7 +961,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,7 +982,7 @@
         <v>128985897</v>
       </c>
       <c r="B5" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>128985884</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98681</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>128985900</v>
       </c>
       <c r="B7" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>128985886</v>
       </c>
       <c r="B8" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>128985888</v>
       </c>
       <c r="B9" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>128985887</v>
       </c>
       <c r="B10" t="n">
-        <v>105706</v>
+        <v>105709</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>128985901</v>
       </c>
       <c r="B11" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128985898</v>
       </c>
       <c r="B12" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128985907</v>
       </c>
       <c r="B13" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985879</v>
+        <v>128985908</v>
       </c>
       <c r="B15" t="n">
-        <v>92852</v>
+        <v>86957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1968,37 +1968,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720754</v>
+        <v>720504</v>
       </c>
       <c r="R15" t="n">
-        <v>6626384</v>
+        <v>6626377</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2039,7 +2036,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2058,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985876</v>
+        <v>128985879</v>
       </c>
       <c r="B16" t="n">
-        <v>92461</v>
+        <v>92855</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,34 +2065,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720766</v>
+        <v>720754</v>
       </c>
       <c r="R16" t="n">
-        <v>6626378</v>
+        <v>6626384</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2137,6 +2136,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2155,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985908</v>
+        <v>128985876</v>
       </c>
       <c r="B17" t="n">
-        <v>86954</v>
+        <v>92464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2166,21 +2166,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720504</v>
+        <v>720766</v>
       </c>
       <c r="R17" t="n">
-        <v>6626377</v>
+        <v>6626378</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2255,7 +2255,7 @@
         <v>128985885</v>
       </c>
       <c r="B18" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128985895</v>
       </c>
       <c r="B19" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,10 +2454,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B20" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R20" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2555,45 +2555,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985873</v>
+        <v>128985875</v>
       </c>
       <c r="B21" t="n">
-        <v>86870</v>
+        <v>92855</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720771</v>
+        <v>720769</v>
       </c>
       <c r="R21" t="n">
-        <v>6626378</v>
+        <v>6626395</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2634,6 +2637,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2652,45 +2656,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985902</v>
+        <v>128985882</v>
       </c>
       <c r="B22" t="n">
-        <v>92461</v>
+        <v>91896</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>1506</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720521</v>
+        <v>720643</v>
       </c>
       <c r="R22" t="n">
-        <v>6626387</v>
+        <v>6626413</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2725,6 +2732,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2733,6 +2745,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2749,10 +2781,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985882</v>
+        <v>128985873</v>
       </c>
       <c r="B23" t="n">
-        <v>91893</v>
+        <v>86873</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2760,37 +2792,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1506</v>
+        <v>445</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720643</v>
+        <v>720771</v>
       </c>
       <c r="R23" t="n">
-        <v>6626413</v>
+        <v>6626378</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2825,11 +2854,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2838,26 +2862,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2874,10 +2878,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B24" t="n">
-        <v>92852</v>
+        <v>92464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,37 +2889,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R24" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2956,7 +2957,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -781,48 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B3" t="n">
-        <v>92855</v>
+        <v>92837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R3" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,7 +860,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,45 +878,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B4" t="n">
-        <v>92837</v>
+        <v>92855</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R4" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -961,6 +960,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985900</v>
+        <v>128985886</v>
       </c>
       <c r="B7" t="n">
         <v>92464</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720544</v>
+        <v>720581</v>
       </c>
       <c r="R7" t="n">
         <v>6626397</v>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985886</v>
+        <v>128985900</v>
       </c>
       <c r="B8" t="n">
         <v>92464</v>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720581</v>
+        <v>720544</v>
       </c>
       <c r="R8" t="n">
         <v>6626397</v>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985908</v>
+        <v>128985876</v>
       </c>
       <c r="B15" t="n">
-        <v>86957</v>
+        <v>92464</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720504</v>
+        <v>720766</v>
       </c>
       <c r="R15" t="n">
-        <v>6626377</v>
+        <v>6626378</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985879</v>
+        <v>128985908</v>
       </c>
       <c r="B16" t="n">
-        <v>92855</v>
+        <v>86957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2065,37 +2065,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720754</v>
+        <v>720504</v>
       </c>
       <c r="R16" t="n">
-        <v>6626384</v>
+        <v>6626377</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2136,7 +2133,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2155,10 +2151,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985876</v>
+        <v>128985879</v>
       </c>
       <c r="B17" t="n">
-        <v>92464</v>
+        <v>92855</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2166,34 +2162,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720766</v>
+        <v>720754</v>
       </c>
       <c r="R17" t="n">
-        <v>6626378</v>
+        <v>6626384</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2234,6 +2233,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2656,48 +2656,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985882</v>
+        <v>128985902</v>
       </c>
       <c r="B22" t="n">
-        <v>91896</v>
+        <v>92464</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1506</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720643</v>
+        <v>720521</v>
       </c>
       <c r="R22" t="n">
-        <v>6626413</v>
+        <v>6626387</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2732,11 +2729,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2745,26 +2737,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2878,45 +2850,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985902</v>
+        <v>128985882</v>
       </c>
       <c r="B24" t="n">
-        <v>92464</v>
+        <v>91896</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>1506</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720521</v>
+        <v>720643</v>
       </c>
       <c r="R24" t="n">
-        <v>6626387</v>
+        <v>6626413</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2951,6 +2926,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -2959,6 +2939,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -2454,10 +2454,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B20" t="n">
-        <v>92855</v>
+        <v>92464</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2465,37 +2465,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R20" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2536,7 +2533,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2555,7 +2551,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B21" t="n">
         <v>92855</v>
@@ -2593,10 +2589,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R21" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2656,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985902</v>
+        <v>128985875</v>
       </c>
       <c r="B22" t="n">
-        <v>92464</v>
+        <v>92855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2667,34 +2663,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720521</v>
+        <v>720769</v>
       </c>
       <c r="R22" t="n">
-        <v>6626387</v>
+        <v>6626395</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2735,6 +2734,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -781,45 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B3" t="n">
-        <v>92837</v>
+        <v>92855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R3" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,6 +863,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -878,48 +882,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B4" t="n">
-        <v>92855</v>
+        <v>92837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R4" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -960,7 +961,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128985897</v>
+        <v>128985884</v>
       </c>
       <c r="B5" t="n">
-        <v>92855</v>
+        <v>98681</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,37 +990,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720543</v>
+        <v>720568</v>
       </c>
       <c r="R5" t="n">
-        <v>6626360</v>
+        <v>6626387</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1061,7 +1058,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1080,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B6" t="n">
-        <v>98681</v>
+        <v>92855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,34 +1087,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R6" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1159,6 +1158,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985886</v>
+        <v>128985900</v>
       </c>
       <c r="B7" t="n">
         <v>92464</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720581</v>
+        <v>720544</v>
       </c>
       <c r="R7" t="n">
         <v>6626397</v>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985900</v>
+        <v>128985886</v>
       </c>
       <c r="B8" t="n">
         <v>92464</v>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720544</v>
+        <v>720581</v>
       </c>
       <c r="R8" t="n">
         <v>6626397</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985908</v>
+        <v>128985879</v>
       </c>
       <c r="B16" t="n">
-        <v>86957</v>
+        <v>92855</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2065,34 +2065,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1988</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720504</v>
+        <v>720754</v>
       </c>
       <c r="R16" t="n">
-        <v>6626377</v>
+        <v>6626384</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2133,6 +2136,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2151,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985879</v>
+        <v>128985908</v>
       </c>
       <c r="B17" t="n">
-        <v>92855</v>
+        <v>86957</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2162,37 +2166,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720754</v>
+        <v>720504</v>
       </c>
       <c r="R17" t="n">
-        <v>6626384</v>
+        <v>6626377</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2233,7 +2234,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2454,32 +2454,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985902</v>
+        <v>128985873</v>
       </c>
       <c r="B20" t="n">
-        <v>92464</v>
+        <v>86873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>445</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720521</v>
+        <v>720771</v>
       </c>
       <c r="R20" t="n">
-        <v>6626387</v>
+        <v>6626378</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985873</v>
+        <v>128985882</v>
       </c>
       <c r="B23" t="n">
-        <v>86873</v>
+        <v>91896</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2764,34 +2764,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>445</v>
+        <v>1506</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720771</v>
+        <v>720643</v>
       </c>
       <c r="R23" t="n">
-        <v>6626378</v>
+        <v>6626413</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2826,6 +2829,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2834,6 +2842,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2850,48 +2878,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985882</v>
+        <v>128985902</v>
       </c>
       <c r="B24" t="n">
-        <v>91896</v>
+        <v>92464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1506</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720643</v>
+        <v>720521</v>
       </c>
       <c r="R24" t="n">
-        <v>6626413</v>
+        <v>6626387</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2926,11 +2951,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -2939,26 +2959,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -781,48 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B3" t="n">
-        <v>92855</v>
+        <v>92844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R3" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,7 +860,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,45 +878,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B4" t="n">
-        <v>92837</v>
+        <v>92862</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R4" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -961,6 +960,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,7 +982,7 @@
         <v>128985884</v>
       </c>
       <c r="B5" t="n">
-        <v>98681</v>
+        <v>98691</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128985897</v>
       </c>
       <c r="B6" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>128985900</v>
       </c>
       <c r="B7" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>128985886</v>
       </c>
       <c r="B8" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>128985888</v>
       </c>
       <c r="B9" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>128985887</v>
       </c>
       <c r="B10" t="n">
-        <v>105709</v>
+        <v>105719</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>128985901</v>
       </c>
       <c r="B11" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128985898</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128985907</v>
       </c>
       <c r="B13" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>128985893</v>
       </c>
       <c r="B14" t="n">
-        <v>58582</v>
+        <v>58584</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985876</v>
+        <v>128985908</v>
       </c>
       <c r="B15" t="n">
-        <v>92464</v>
+        <v>86961</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>1988</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720766</v>
+        <v>720504</v>
       </c>
       <c r="R15" t="n">
-        <v>6626378</v>
+        <v>6626377</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985879</v>
+        <v>128985876</v>
       </c>
       <c r="B16" t="n">
-        <v>92855</v>
+        <v>92471</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2065,37 +2065,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720754</v>
+        <v>720766</v>
       </c>
       <c r="R16" t="n">
-        <v>6626384</v>
+        <v>6626378</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2136,7 +2133,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2155,10 +2151,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985908</v>
+        <v>128985879</v>
       </c>
       <c r="B17" t="n">
-        <v>86957</v>
+        <v>92862</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2166,34 +2162,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1988</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720504</v>
+        <v>720754</v>
       </c>
       <c r="R17" t="n">
-        <v>6626377</v>
+        <v>6626384</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2234,6 +2233,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>128985885</v>
       </c>
       <c r="B18" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128985895</v>
       </c>
       <c r="B19" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,10 +2454,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985873</v>
+        <v>128985882</v>
       </c>
       <c r="B20" t="n">
-        <v>86873</v>
+        <v>91903</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2465,34 +2465,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>445</v>
+        <v>1506</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720771</v>
+        <v>720643</v>
       </c>
       <c r="R20" t="n">
-        <v>6626378</v>
+        <v>6626413</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2527,6 +2530,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2535,6 +2543,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2551,10 +2579,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B21" t="n">
-        <v>92855</v>
+        <v>92471</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2562,37 +2590,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R21" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2633,7 +2658,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2676,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B22" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2690,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R22" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2753,32 +2777,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985882</v>
+        <v>128985875</v>
       </c>
       <c r="B23" t="n">
-        <v>91896</v>
+        <v>92862</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1506</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2791,10 +2815,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720643</v>
+        <v>720769</v>
       </c>
       <c r="R23" t="n">
-        <v>6626413</v>
+        <v>6626395</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2829,39 +2853,15 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2878,10 +2878,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985902</v>
+        <v>128985899</v>
       </c>
       <c r="B24" t="n">
-        <v>92464</v>
+        <v>58582</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2889,21 +2889,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>208250</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720521</v>
+        <v>720542</v>
       </c>
       <c r="R24" t="n">
-        <v>6626387</v>
+        <v>6626391</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2975,32 +2975,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985899</v>
+        <v>128985873</v>
       </c>
       <c r="B25" t="n">
-        <v>58580</v>
+        <v>86877</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208250</v>
+        <v>445</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720542</v>
+        <v>720771</v>
       </c>
       <c r="R25" t="n">
-        <v>6626391</v>
+        <v>6626378</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B5" t="n">
-        <v>98691</v>
+        <v>92862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,34 +990,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R5" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1058,6 +1061,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1076,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985897</v>
+        <v>128985884</v>
       </c>
       <c r="B6" t="n">
-        <v>92862</v>
+        <v>98691</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,37 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720543</v>
+        <v>720568</v>
       </c>
       <c r="R6" t="n">
-        <v>6626360</v>
+        <v>6626387</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1158,7 +1159,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128985878</v>
       </c>
       <c r="B3" t="n">
-        <v>92844</v>
+        <v>92851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128985894</v>
       </c>
       <c r="B4" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128985897</v>
+        <v>128985884</v>
       </c>
       <c r="B5" t="n">
-        <v>92862</v>
+        <v>98698</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,37 +990,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720543</v>
+        <v>720568</v>
       </c>
       <c r="R5" t="n">
-        <v>6626360</v>
+        <v>6626387</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1061,7 +1058,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1080,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B6" t="n">
-        <v>98691</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,34 +1087,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R6" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1159,6 +1158,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985900</v>
+        <v>128985888</v>
       </c>
       <c r="B7" t="n">
-        <v>92471</v>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,34 +1188,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720544</v>
+        <v>720578</v>
       </c>
       <c r="R7" t="n">
-        <v>6626397</v>
+        <v>6626426</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1256,6 +1259,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1274,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985886</v>
+        <v>128985900</v>
       </c>
       <c r="B8" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1309,7 +1313,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720581</v>
+        <v>720544</v>
       </c>
       <c r="R8" t="n">
         <v>6626397</v>
@@ -1371,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985888</v>
+        <v>128985886</v>
       </c>
       <c r="B9" t="n">
-        <v>92862</v>
+        <v>92478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1382,37 +1386,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720578</v>
+        <v>720581</v>
       </c>
       <c r="R9" t="n">
-        <v>6626426</v>
+        <v>6626397</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1453,7 +1454,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>128985887</v>
       </c>
       <c r="B10" t="n">
-        <v>105719</v>
+        <v>105726</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>128985901</v>
       </c>
       <c r="B11" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128985898</v>
       </c>
       <c r="B12" t="n">
-        <v>91305</v>
+        <v>91312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128985907</v>
       </c>
       <c r="B13" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>128985908</v>
       </c>
       <c r="B15" t="n">
-        <v>86961</v>
+        <v>86968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>128985876</v>
       </c>
       <c r="B16" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>128985879</v>
       </c>
       <c r="B17" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>128985885</v>
       </c>
       <c r="B18" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128985895</v>
       </c>
       <c r="B19" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>128985882</v>
       </c>
       <c r="B20" t="n">
-        <v>91903</v>
+        <v>91910</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2579,32 +2579,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985902</v>
+        <v>128985873</v>
       </c>
       <c r="B21" t="n">
-        <v>92471</v>
+        <v>86884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4769</v>
+        <v>445</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720521</v>
+        <v>720771</v>
       </c>
       <c r="R21" t="n">
-        <v>6626387</v>
+        <v>6626378</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2679,7 +2679,7 @@
         <v>128985896</v>
       </c>
       <c r="B22" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>128985875</v>
       </c>
       <c r="B23" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,10 +2878,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985899</v>
+        <v>128985902</v>
       </c>
       <c r="B24" t="n">
-        <v>58582</v>
+        <v>92478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2889,21 +2889,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>208250</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720542</v>
+        <v>720521</v>
       </c>
       <c r="R24" t="n">
-        <v>6626391</v>
+        <v>6626387</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2975,32 +2975,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985873</v>
+        <v>128985899</v>
       </c>
       <c r="B25" t="n">
-        <v>86877</v>
+        <v>58582</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>445</v>
+        <v>208250</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720771</v>
+        <v>720542</v>
       </c>
       <c r="R25" t="n">
-        <v>6626378</v>
+        <v>6626391</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -781,45 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B3" t="n">
-        <v>92851</v>
+        <v>92871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R3" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,6 +863,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -878,48 +882,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>92853</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R4" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -960,7 +961,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B5" t="n">
-        <v>98698</v>
+        <v>92871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,34 +990,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R5" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1058,6 +1061,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1076,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985897</v>
+        <v>128985884</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>98700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,37 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720543</v>
+        <v>720568</v>
       </c>
       <c r="R6" t="n">
-        <v>6626360</v>
+        <v>6626387</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1158,7 +1159,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985888</v>
+        <v>128985900</v>
       </c>
       <c r="B7" t="n">
-        <v>92869</v>
+        <v>92480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,37 +1188,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720578</v>
+        <v>720544</v>
       </c>
       <c r="R7" t="n">
-        <v>6626426</v>
+        <v>6626397</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1259,7 +1256,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1278,10 +1274,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985900</v>
+        <v>128985886</v>
       </c>
       <c r="B8" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,7 +1309,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720544</v>
+        <v>720581</v>
       </c>
       <c r="R8" t="n">
         <v>6626397</v>
@@ -1375,10 +1371,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985886</v>
+        <v>128985888</v>
       </c>
       <c r="B9" t="n">
-        <v>92478</v>
+        <v>92871</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,34 +1382,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720581</v>
+        <v>720578</v>
       </c>
       <c r="R9" t="n">
-        <v>6626397</v>
+        <v>6626426</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1454,6 +1453,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>128985887</v>
       </c>
       <c r="B10" t="n">
-        <v>105726</v>
+        <v>105728</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>128985901</v>
       </c>
       <c r="B11" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128985898</v>
       </c>
       <c r="B12" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128985907</v>
       </c>
       <c r="B13" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>128985893</v>
       </c>
       <c r="B14" t="n">
-        <v>58584</v>
+        <v>58586</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>128985908</v>
       </c>
       <c r="B15" t="n">
-        <v>86968</v>
+        <v>86970</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>128985876</v>
       </c>
       <c r="B16" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>128985879</v>
       </c>
       <c r="B17" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>128985885</v>
       </c>
       <c r="B18" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128985895</v>
       </c>
       <c r="B19" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,32 +2454,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985882</v>
+        <v>128985896</v>
       </c>
       <c r="B20" t="n">
-        <v>91910</v>
+        <v>92871</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1506</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720643</v>
+        <v>720577</v>
       </c>
       <c r="R20" t="n">
-        <v>6626413</v>
+        <v>6626370</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2530,39 +2530,15 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2579,45 +2555,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985873</v>
+        <v>128985875</v>
       </c>
       <c r="B21" t="n">
-        <v>86884</v>
+        <v>92871</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720771</v>
+        <v>720769</v>
       </c>
       <c r="R21" t="n">
-        <v>6626378</v>
+        <v>6626395</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2658,6 +2637,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2676,10 +2656,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985896</v>
+        <v>128985899</v>
       </c>
       <c r="B22" t="n">
-        <v>92869</v>
+        <v>58584</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2687,37 +2667,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>208250</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720577</v>
+        <v>720542</v>
       </c>
       <c r="R22" t="n">
-        <v>6626370</v>
+        <v>6626391</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2758,7 +2735,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2777,32 +2753,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985875</v>
+        <v>128985882</v>
       </c>
       <c r="B23" t="n">
-        <v>92869</v>
+        <v>91912</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>1506</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2815,10 +2791,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720769</v>
+        <v>720643</v>
       </c>
       <c r="R23" t="n">
-        <v>6626395</v>
+        <v>6626413</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2853,15 +2829,39 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2881,7 +2881,7 @@
         <v>128985902</v>
       </c>
       <c r="B24" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2975,32 +2975,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985899</v>
+        <v>128985873</v>
       </c>
       <c r="B25" t="n">
-        <v>58582</v>
+        <v>86886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208250</v>
+        <v>445</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720542</v>
+        <v>720771</v>
       </c>
       <c r="R25" t="n">
-        <v>6626391</v>
+        <v>6626378</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -781,48 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B3" t="n">
-        <v>92871</v>
+        <v>92853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R3" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,7 +860,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,45 +878,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B4" t="n">
-        <v>92853</v>
+        <v>92871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R4" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -961,6 +960,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985908</v>
+        <v>128985876</v>
       </c>
       <c r="B15" t="n">
-        <v>86970</v>
+        <v>92480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720504</v>
+        <v>720766</v>
       </c>
       <c r="R15" t="n">
-        <v>6626377</v>
+        <v>6626378</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985876</v>
+        <v>128985908</v>
       </c>
       <c r="B16" t="n">
-        <v>92480</v>
+        <v>86970</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2065,21 +2065,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>1988</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720766</v>
+        <v>720504</v>
       </c>
       <c r="R16" t="n">
-        <v>6626378</v>
+        <v>6626377</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2454,10 +2454,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B20" t="n">
-        <v>92871</v>
+        <v>92480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2465,37 +2465,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R20" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2536,7 +2533,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2555,10 +2551,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985875</v>
+        <v>128985899</v>
       </c>
       <c r="B21" t="n">
-        <v>92871</v>
+        <v>58584</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2566,37 +2562,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>208250</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720769</v>
+        <v>720542</v>
       </c>
       <c r="R21" t="n">
-        <v>6626395</v>
+        <v>6626391</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2637,7 +2630,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2656,32 +2648,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985899</v>
+        <v>128985873</v>
       </c>
       <c r="B22" t="n">
-        <v>58584</v>
+        <v>86886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208250</v>
+        <v>445</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2691,10 +2683,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720542</v>
+        <v>720771</v>
       </c>
       <c r="R22" t="n">
-        <v>6626391</v>
+        <v>6626378</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2878,10 +2870,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985902</v>
+        <v>128985896</v>
       </c>
       <c r="B24" t="n">
-        <v>92480</v>
+        <v>92871</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2889,34 +2881,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720521</v>
+        <v>720577</v>
       </c>
       <c r="R24" t="n">
-        <v>6626387</v>
+        <v>6626370</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2957,6 +2952,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2975,45 +2971,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985873</v>
+        <v>128985875</v>
       </c>
       <c r="B25" t="n">
-        <v>86886</v>
+        <v>92871</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720771</v>
+        <v>720769</v>
       </c>
       <c r="R25" t="n">
-        <v>6626378</v>
+        <v>6626395</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3054,6 +3053,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -2454,32 +2454,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985902</v>
+        <v>128985873</v>
       </c>
       <c r="B20" t="n">
-        <v>92480</v>
+        <v>86886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>445</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720521</v>
+        <v>720771</v>
       </c>
       <c r="R20" t="n">
-        <v>6626387</v>
+        <v>6626378</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2551,45 +2551,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985899</v>
+        <v>128985882</v>
       </c>
       <c r="B21" t="n">
-        <v>58584</v>
+        <v>91912</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208250</v>
+        <v>1506</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720542</v>
+        <v>720643</v>
       </c>
       <c r="R21" t="n">
-        <v>6626391</v>
+        <v>6626413</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2624,6 +2627,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2632,6 +2640,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2648,45 +2676,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985873</v>
+        <v>128985896</v>
       </c>
       <c r="B22" t="n">
-        <v>86886</v>
+        <v>92871</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720771</v>
+        <v>720577</v>
       </c>
       <c r="R22" t="n">
-        <v>6626378</v>
+        <v>6626370</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2727,6 +2758,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2745,32 +2777,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985882</v>
+        <v>128985875</v>
       </c>
       <c r="B23" t="n">
-        <v>91912</v>
+        <v>92871</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1506</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2783,10 +2815,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720643</v>
+        <v>720769</v>
       </c>
       <c r="R23" t="n">
-        <v>6626413</v>
+        <v>6626395</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2821,39 +2853,15 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2870,10 +2878,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B24" t="n">
-        <v>92871</v>
+        <v>92480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2881,37 +2889,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R24" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2952,7 +2957,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2971,10 +2975,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985875</v>
+        <v>128985899</v>
       </c>
       <c r="B25" t="n">
-        <v>92871</v>
+        <v>58584</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2982,37 +2986,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>208250</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720769</v>
+        <v>720542</v>
       </c>
       <c r="R25" t="n">
-        <v>6626395</v>
+        <v>6626391</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3053,7 +3054,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128985878</v>
       </c>
       <c r="B3" t="n">
-        <v>92853</v>
+        <v>92839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128985894</v>
       </c>
       <c r="B4" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>128985897</v>
       </c>
       <c r="B5" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>128985884</v>
       </c>
       <c r="B6" t="n">
-        <v>98700</v>
+        <v>98726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>128985900</v>
       </c>
       <c r="B7" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>128985886</v>
       </c>
       <c r="B8" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>128985888</v>
       </c>
       <c r="B9" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>128985887</v>
       </c>
       <c r="B10" t="n">
-        <v>105728</v>
+        <v>105754</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>128985901</v>
       </c>
       <c r="B11" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128985898</v>
       </c>
       <c r="B12" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128985907</v>
       </c>
       <c r="B13" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985876</v>
+        <v>128985879</v>
       </c>
       <c r="B15" t="n">
-        <v>92480</v>
+        <v>92857</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1968,34 +1968,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720766</v>
+        <v>720754</v>
       </c>
       <c r="R15" t="n">
-        <v>6626378</v>
+        <v>6626384</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2036,6 +2039,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2054,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985908</v>
+        <v>128985876</v>
       </c>
       <c r="B16" t="n">
-        <v>86970</v>
+        <v>92494</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2065,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2089,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720504</v>
+        <v>720766</v>
       </c>
       <c r="R16" t="n">
-        <v>6626377</v>
+        <v>6626378</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2151,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985879</v>
+        <v>128985908</v>
       </c>
       <c r="B17" t="n">
-        <v>92871</v>
+        <v>86971</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2162,37 +2166,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720754</v>
+        <v>720504</v>
       </c>
       <c r="R17" t="n">
-        <v>6626384</v>
+        <v>6626377</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2233,7 +2234,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>128985885</v>
       </c>
       <c r="B18" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128985895</v>
       </c>
       <c r="B19" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,32 +2454,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985873</v>
+        <v>128985902</v>
       </c>
       <c r="B20" t="n">
-        <v>86886</v>
+        <v>92494</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>445</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720771</v>
+        <v>720521</v>
       </c>
       <c r="R20" t="n">
-        <v>6626378</v>
+        <v>6626387</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2554,7 +2554,7 @@
         <v>128985882</v>
       </c>
       <c r="B21" t="n">
-        <v>91912</v>
+        <v>91921</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,48 +2676,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985896</v>
+        <v>128985873</v>
       </c>
       <c r="B22" t="n">
-        <v>92871</v>
+        <v>86887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>445</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720577</v>
+        <v>720771</v>
       </c>
       <c r="R22" t="n">
-        <v>6626370</v>
+        <v>6626378</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2758,7 +2755,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2777,10 +2773,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B23" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2815,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R23" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2878,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985902</v>
+        <v>128985875</v>
       </c>
       <c r="B24" t="n">
-        <v>92480</v>
+        <v>92857</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2889,34 +2885,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720521</v>
+        <v>720769</v>
       </c>
       <c r="R24" t="n">
-        <v>6626387</v>
+        <v>6626395</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2957,6 +2956,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -781,45 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B3" t="n">
-        <v>92839</v>
+        <v>92858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R3" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,6 +863,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -878,48 +882,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B4" t="n">
-        <v>92857</v>
+        <v>92840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R4" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -960,7 +961,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128985897</v>
+        <v>128985884</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,37 +990,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720543</v>
+        <v>720568</v>
       </c>
       <c r="R5" t="n">
-        <v>6626360</v>
+        <v>6626387</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1061,7 +1058,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1080,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B6" t="n">
-        <v>98726</v>
+        <v>92858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,34 +1087,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R6" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1159,6 +1158,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>128985900</v>
       </c>
       <c r="B7" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>128985886</v>
       </c>
       <c r="B8" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>128985888</v>
       </c>
       <c r="B9" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>128985887</v>
       </c>
       <c r="B10" t="n">
-        <v>105754</v>
+        <v>105756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>128985901</v>
       </c>
       <c r="B11" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128985907</v>
       </c>
       <c r="B13" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>128985879</v>
       </c>
       <c r="B15" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985876</v>
+        <v>128985908</v>
       </c>
       <c r="B16" t="n">
-        <v>92494</v>
+        <v>86971</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>1988</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720766</v>
+        <v>720504</v>
       </c>
       <c r="R16" t="n">
-        <v>6626378</v>
+        <v>6626377</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2155,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985908</v>
+        <v>128985876</v>
       </c>
       <c r="B17" t="n">
-        <v>86971</v>
+        <v>92495</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2166,21 +2166,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720504</v>
+        <v>720766</v>
       </c>
       <c r="R17" t="n">
-        <v>6626377</v>
+        <v>6626378</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2255,7 +2255,7 @@
         <v>128985885</v>
       </c>
       <c r="B18" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128985895</v>
       </c>
       <c r="B19" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,32 +2454,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985902</v>
+        <v>128985873</v>
       </c>
       <c r="B20" t="n">
-        <v>92494</v>
+        <v>86887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>445</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720521</v>
+        <v>720771</v>
       </c>
       <c r="R20" t="n">
-        <v>6626387</v>
+        <v>6626378</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2551,48 +2551,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985882</v>
+        <v>128985902</v>
       </c>
       <c r="B21" t="n">
-        <v>91921</v>
+        <v>92495</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1506</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720643</v>
+        <v>720521</v>
       </c>
       <c r="R21" t="n">
-        <v>6626413</v>
+        <v>6626387</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2627,11 +2624,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2640,26 +2632,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2676,45 +2648,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985873</v>
+        <v>128985896</v>
       </c>
       <c r="B22" t="n">
-        <v>86887</v>
+        <v>92858</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720771</v>
+        <v>720577</v>
       </c>
       <c r="R22" t="n">
-        <v>6626378</v>
+        <v>6626370</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2755,6 +2730,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2773,10 +2749,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985896</v>
+        <v>128985875</v>
       </c>
       <c r="B23" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2811,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720577</v>
+        <v>720769</v>
       </c>
       <c r="R23" t="n">
-        <v>6626370</v>
+        <v>6626395</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2874,32 +2850,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985875</v>
+        <v>128985882</v>
       </c>
       <c r="B24" t="n">
-        <v>92857</v>
+        <v>91922</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>1506</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2912,10 +2888,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720769</v>
+        <v>720643</v>
       </c>
       <c r="R24" t="n">
-        <v>6626395</v>
+        <v>6626413</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2950,15 +2926,39 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>92858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,34 +990,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R5" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1058,6 +1061,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1076,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985897</v>
+        <v>128985884</v>
       </c>
       <c r="B6" t="n">
-        <v>92858</v>
+        <v>98728</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,37 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720543</v>
+        <v>720568</v>
       </c>
       <c r="R6" t="n">
-        <v>6626360</v>
+        <v>6626387</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1158,7 +1159,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985900</v>
+        <v>128985888</v>
       </c>
       <c r="B7" t="n">
-        <v>92495</v>
+        <v>92858</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,34 +1188,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720544</v>
+        <v>720578</v>
       </c>
       <c r="R7" t="n">
-        <v>6626397</v>
+        <v>6626426</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1256,6 +1259,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1274,7 +1278,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985886</v>
+        <v>128985900</v>
       </c>
       <c r="B8" t="n">
         <v>92495</v>
@@ -1309,7 +1313,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720581</v>
+        <v>720544</v>
       </c>
       <c r="R8" t="n">
         <v>6626397</v>
@@ -1371,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985888</v>
+        <v>128985886</v>
       </c>
       <c r="B9" t="n">
-        <v>92858</v>
+        <v>92495</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1382,37 +1386,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720578</v>
+        <v>720581</v>
       </c>
       <c r="R9" t="n">
-        <v>6626426</v>
+        <v>6626397</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1453,7 +1454,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>128985887</v>
       </c>
       <c r="B10" t="n">
-        <v>105756</v>
+        <v>105757</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128985907</v>
       </c>
       <c r="B13" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2454,45 +2454,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985873</v>
+        <v>128985896</v>
       </c>
       <c r="B20" t="n">
-        <v>86887</v>
+        <v>92858</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720771</v>
+        <v>720577</v>
       </c>
       <c r="R20" t="n">
-        <v>6626378</v>
+        <v>6626370</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2533,6 +2536,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2551,10 +2555,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985902</v>
+        <v>128985875</v>
       </c>
       <c r="B21" t="n">
-        <v>92495</v>
+        <v>92858</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2562,34 +2566,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720521</v>
+        <v>720769</v>
       </c>
       <c r="R21" t="n">
-        <v>6626387</v>
+        <v>6626395</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2630,6 +2637,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2648,10 +2656,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B22" t="n">
-        <v>92858</v>
+        <v>92495</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2659,37 +2667,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R22" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2730,7 +2735,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2749,10 +2753,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985875</v>
+        <v>128985899</v>
       </c>
       <c r="B23" t="n">
-        <v>92858</v>
+        <v>58584</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2760,37 +2764,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>208250</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720769</v>
+        <v>720542</v>
       </c>
       <c r="R23" t="n">
-        <v>6626395</v>
+        <v>6626391</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2831,7 +2832,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985882</v>
+        <v>128985873</v>
       </c>
       <c r="B24" t="n">
-        <v>91922</v>
+        <v>86887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2861,37 +2861,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1506</v>
+        <v>445</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720643</v>
+        <v>720771</v>
       </c>
       <c r="R24" t="n">
-        <v>6626413</v>
+        <v>6626378</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2926,11 +2923,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -2939,26 +2931,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -2975,45 +2947,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985899</v>
+        <v>128985882</v>
       </c>
       <c r="B25" t="n">
-        <v>58584</v>
+        <v>91922</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208250</v>
+        <v>1506</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720542</v>
+        <v>720643</v>
       </c>
       <c r="R25" t="n">
-        <v>6626391</v>
+        <v>6626413</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3048,6 +3023,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3056,6 +3036,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128985894</v>
       </c>
       <c r="B3" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128985878</v>
       </c>
       <c r="B4" t="n">
-        <v>92840</v>
+        <v>92843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128985897</v>
+        <v>128985884</v>
       </c>
       <c r="B5" t="n">
-        <v>92858</v>
+        <v>98732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,37 +990,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720543</v>
+        <v>720568</v>
       </c>
       <c r="R5" t="n">
-        <v>6626360</v>
+        <v>6626387</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1061,7 +1058,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1080,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B6" t="n">
-        <v>98728</v>
+        <v>92861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,34 +1087,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R6" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1159,6 +1158,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985888</v>
+        <v>128985900</v>
       </c>
       <c r="B7" t="n">
-        <v>92858</v>
+        <v>92498</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,37 +1188,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720578</v>
+        <v>720544</v>
       </c>
       <c r="R7" t="n">
-        <v>6626426</v>
+        <v>6626397</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1259,7 +1256,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1278,10 +1274,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985900</v>
+        <v>128985886</v>
       </c>
       <c r="B8" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,7 +1309,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720544</v>
+        <v>720581</v>
       </c>
       <c r="R8" t="n">
         <v>6626397</v>
@@ -1375,10 +1371,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985886</v>
+        <v>128985888</v>
       </c>
       <c r="B9" t="n">
-        <v>92495</v>
+        <v>92861</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,34 +1382,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720581</v>
+        <v>720578</v>
       </c>
       <c r="R9" t="n">
-        <v>6626397</v>
+        <v>6626426</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1454,6 +1453,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>128985887</v>
       </c>
       <c r="B10" t="n">
-        <v>105757</v>
+        <v>105761</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>128985901</v>
       </c>
       <c r="B11" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128985898</v>
       </c>
       <c r="B12" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128985907</v>
       </c>
       <c r="B13" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985879</v>
+        <v>128985908</v>
       </c>
       <c r="B15" t="n">
-        <v>92858</v>
+        <v>86974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1968,37 +1968,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720754</v>
+        <v>720504</v>
       </c>
       <c r="R15" t="n">
-        <v>6626384</v>
+        <v>6626377</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2039,7 +2036,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2058,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985908</v>
+        <v>128985876</v>
       </c>
       <c r="B16" t="n">
-        <v>86971</v>
+        <v>92498</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,21 +2065,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2089,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720504</v>
+        <v>720766</v>
       </c>
       <c r="R16" t="n">
-        <v>6626377</v>
+        <v>6626378</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2155,10 +2151,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985876</v>
+        <v>128985879</v>
       </c>
       <c r="B17" t="n">
-        <v>92495</v>
+        <v>92861</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2166,34 +2162,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720766</v>
+        <v>720754</v>
       </c>
       <c r="R17" t="n">
-        <v>6626378</v>
+        <v>6626384</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2234,6 +2233,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>128985885</v>
       </c>
       <c r="B18" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128985895</v>
       </c>
       <c r="B19" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,10 +2454,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985896</v>
+        <v>128985902</v>
       </c>
       <c r="B20" t="n">
-        <v>92858</v>
+        <v>92498</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2465,37 +2465,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720577</v>
+        <v>720521</v>
       </c>
       <c r="R20" t="n">
-        <v>6626370</v>
+        <v>6626387</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2536,7 +2533,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2555,10 +2551,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B21" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,10 +2589,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R21" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2656,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985902</v>
+        <v>128985875</v>
       </c>
       <c r="B22" t="n">
-        <v>92495</v>
+        <v>92861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2667,34 +2663,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720521</v>
+        <v>720769</v>
       </c>
       <c r="R22" t="n">
-        <v>6626387</v>
+        <v>6626395</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2735,6 +2734,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2753,45 +2753,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985899</v>
+        <v>128985882</v>
       </c>
       <c r="B23" t="n">
-        <v>58584</v>
+        <v>91925</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>208250</v>
+        <v>1506</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720542</v>
+        <v>720643</v>
       </c>
       <c r="R23" t="n">
-        <v>6626391</v>
+        <v>6626413</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2826,6 +2829,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2834,6 +2842,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2853,7 +2881,7 @@
         <v>128985873</v>
       </c>
       <c r="B24" t="n">
-        <v>86887</v>
+        <v>86890</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,48 +2975,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985882</v>
+        <v>128985899</v>
       </c>
       <c r="B25" t="n">
-        <v>91922</v>
+        <v>58584</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1506</v>
+        <v>208250</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720643</v>
+        <v>720542</v>
       </c>
       <c r="R25" t="n">
-        <v>6626413</v>
+        <v>6626391</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3023,11 +3048,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3036,26 +3056,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -781,48 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B3" t="n">
-        <v>92861</v>
+        <v>92845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R3" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,7 +860,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,45 +878,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B4" t="n">
-        <v>92843</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R4" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -961,6 +960,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,7 +982,7 @@
         <v>128985884</v>
       </c>
       <c r="B5" t="n">
-        <v>98732</v>
+        <v>98734</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128985897</v>
       </c>
       <c r="B6" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985900</v>
+        <v>128985888</v>
       </c>
       <c r="B7" t="n">
-        <v>92498</v>
+        <v>92863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,34 +1188,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720544</v>
+        <v>720578</v>
       </c>
       <c r="R7" t="n">
-        <v>6626397</v>
+        <v>6626426</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1256,6 +1259,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1274,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985886</v>
+        <v>128985900</v>
       </c>
       <c r="B8" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1309,7 +1313,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720581</v>
+        <v>720544</v>
       </c>
       <c r="R8" t="n">
         <v>6626397</v>
@@ -1371,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985888</v>
+        <v>128985886</v>
       </c>
       <c r="B9" t="n">
-        <v>92861</v>
+        <v>92500</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1382,37 +1386,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720578</v>
+        <v>720581</v>
       </c>
       <c r="R9" t="n">
-        <v>6626426</v>
+        <v>6626397</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1453,7 +1454,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>128985887</v>
       </c>
       <c r="B10" t="n">
-        <v>105761</v>
+        <v>105763</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>128985901</v>
       </c>
       <c r="B11" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128985898</v>
       </c>
       <c r="B12" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128985907</v>
       </c>
       <c r="B13" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>128985908</v>
       </c>
       <c r="B15" t="n">
-        <v>86974</v>
+        <v>86976</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985876</v>
+        <v>128985879</v>
       </c>
       <c r="B16" t="n">
-        <v>92498</v>
+        <v>92863</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2065,34 +2065,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720766</v>
+        <v>720754</v>
       </c>
       <c r="R16" t="n">
-        <v>6626378</v>
+        <v>6626384</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2133,6 +2136,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2151,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985879</v>
+        <v>128985876</v>
       </c>
       <c r="B17" t="n">
-        <v>92861</v>
+        <v>92500</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2162,37 +2166,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720754</v>
+        <v>720766</v>
       </c>
       <c r="R17" t="n">
-        <v>6626384</v>
+        <v>6626378</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2233,7 +2234,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>128985885</v>
       </c>
       <c r="B18" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>128985895</v>
       </c>
       <c r="B19" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,32 +2454,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985902</v>
+        <v>128985873</v>
       </c>
       <c r="B20" t="n">
-        <v>92498</v>
+        <v>86892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>445</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720521</v>
+        <v>720771</v>
       </c>
       <c r="R20" t="n">
-        <v>6626387</v>
+        <v>6626378</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2551,32 +2551,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985896</v>
+        <v>128985882</v>
       </c>
       <c r="B21" t="n">
-        <v>92861</v>
+        <v>91927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>1506</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720577</v>
+        <v>720643</v>
       </c>
       <c r="R21" t="n">
-        <v>6626370</v>
+        <v>6626413</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2627,15 +2627,39 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2652,10 +2676,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B22" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2690,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R22" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2753,32 +2777,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985882</v>
+        <v>128985875</v>
       </c>
       <c r="B23" t="n">
-        <v>91925</v>
+        <v>92863</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1506</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2791,10 +2815,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720643</v>
+        <v>720769</v>
       </c>
       <c r="R23" t="n">
-        <v>6626413</v>
+        <v>6626395</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2829,39 +2853,15 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2878,32 +2878,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985873</v>
+        <v>128985902</v>
       </c>
       <c r="B24" t="n">
-        <v>86890</v>
+        <v>92500</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>445</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720771</v>
+        <v>720521</v>
       </c>
       <c r="R24" t="n">
-        <v>6626378</v>
+        <v>6626387</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128985878</v>
       </c>
       <c r="B3" t="n">
-        <v>92845</v>
+        <v>92849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128985894</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B5" t="n">
-        <v>98734</v>
+        <v>92867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,34 +990,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R5" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1058,6 +1061,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1076,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985897</v>
+        <v>128985884</v>
       </c>
       <c r="B6" t="n">
-        <v>92863</v>
+        <v>98738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,37 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720543</v>
+        <v>720568</v>
       </c>
       <c r="R6" t="n">
-        <v>6626360</v>
+        <v>6626387</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1158,7 +1159,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>128985888</v>
       </c>
       <c r="B7" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985900</v>
+        <v>128985886</v>
       </c>
       <c r="B8" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720544</v>
+        <v>720581</v>
       </c>
       <c r="R8" t="n">
         <v>6626397</v>
@@ -1375,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985886</v>
+        <v>128985900</v>
       </c>
       <c r="B9" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720581</v>
+        <v>720544</v>
       </c>
       <c r="R9" t="n">
         <v>6626397</v>
@@ -1475,7 +1475,7 @@
         <v>128985887</v>
       </c>
       <c r="B10" t="n">
-        <v>105763</v>
+        <v>105767</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>128985901</v>
       </c>
       <c r="B11" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128985898</v>
       </c>
       <c r="B12" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128985907</v>
       </c>
       <c r="B13" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>128985908</v>
       </c>
       <c r="B15" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>128985879</v>
       </c>
       <c r="B16" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>128985876</v>
       </c>
       <c r="B17" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985885</v>
+        <v>128985895</v>
       </c>
       <c r="B18" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720573</v>
+        <v>720572</v>
       </c>
       <c r="R18" t="n">
-        <v>6626380</v>
+        <v>6626395</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985895</v>
+        <v>128985885</v>
       </c>
       <c r="B19" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720572</v>
+        <v>720573</v>
       </c>
       <c r="R19" t="n">
-        <v>6626395</v>
+        <v>6626380</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2454,45 +2454,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985873</v>
+        <v>128985896</v>
       </c>
       <c r="B20" t="n">
-        <v>86892</v>
+        <v>92867</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720771</v>
+        <v>720577</v>
       </c>
       <c r="R20" t="n">
-        <v>6626378</v>
+        <v>6626370</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2533,6 +2536,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2551,32 +2555,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985882</v>
+        <v>128985875</v>
       </c>
       <c r="B21" t="n">
-        <v>91927</v>
+        <v>92867</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1506</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2589,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720643</v>
+        <v>720769</v>
       </c>
       <c r="R21" t="n">
-        <v>6626413</v>
+        <v>6626395</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2627,39 +2631,15 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2676,10 +2656,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985896</v>
+        <v>128985899</v>
       </c>
       <c r="B22" t="n">
-        <v>92863</v>
+        <v>58584</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2687,37 +2667,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>208250</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720577</v>
+        <v>720542</v>
       </c>
       <c r="R22" t="n">
-        <v>6626370</v>
+        <v>6626391</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2758,7 +2735,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2777,32 +2753,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985875</v>
+        <v>128985882</v>
       </c>
       <c r="B23" t="n">
-        <v>92863</v>
+        <v>91931</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>1506</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2815,10 +2791,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720769</v>
+        <v>720643</v>
       </c>
       <c r="R23" t="n">
-        <v>6626395</v>
+        <v>6626413</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2853,15 +2829,39 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2878,32 +2878,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985902</v>
+        <v>128985873</v>
       </c>
       <c r="B24" t="n">
-        <v>92500</v>
+        <v>86896</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>445</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720521</v>
+        <v>720771</v>
       </c>
       <c r="R24" t="n">
-        <v>6626387</v>
+        <v>6626378</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2975,10 +2975,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985899</v>
+        <v>128985902</v>
       </c>
       <c r="B25" t="n">
-        <v>58584</v>
+        <v>92504</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2986,21 +2986,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208250</v>
+        <v>4769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720542</v>
+        <v>720521</v>
       </c>
       <c r="R25" t="n">
-        <v>6626391</v>
+        <v>6626387</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128985878</v>
       </c>
       <c r="B3" t="n">
-        <v>92849</v>
+        <v>92850</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128985894</v>
       </c>
       <c r="B4" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128985897</v>
+        <v>128985884</v>
       </c>
       <c r="B5" t="n">
-        <v>92867</v>
+        <v>98746</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,37 +990,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720543</v>
+        <v>720568</v>
       </c>
       <c r="R5" t="n">
-        <v>6626360</v>
+        <v>6626387</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1061,7 +1058,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1080,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B6" t="n">
-        <v>98738</v>
+        <v>92868</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,34 +1087,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R6" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1159,6 +1158,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985888</v>
+        <v>128985900</v>
       </c>
       <c r="B7" t="n">
-        <v>92867</v>
+        <v>92505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1188,37 +1188,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720578</v>
+        <v>720544</v>
       </c>
       <c r="R7" t="n">
-        <v>6626426</v>
+        <v>6626397</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1259,7 +1256,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1281,7 +1277,7 @@
         <v>128985886</v>
       </c>
       <c r="B8" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,10 +1371,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985900</v>
+        <v>128985888</v>
       </c>
       <c r="B9" t="n">
-        <v>92504</v>
+        <v>92868</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,34 +1382,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720544</v>
+        <v>720578</v>
       </c>
       <c r="R9" t="n">
-        <v>6626397</v>
+        <v>6626426</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1454,6 +1453,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>128985887</v>
       </c>
       <c r="B10" t="n">
-        <v>105767</v>
+        <v>105777</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>128985901</v>
       </c>
       <c r="B11" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>128985898</v>
       </c>
       <c r="B12" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128985907</v>
       </c>
       <c r="B13" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985908</v>
+        <v>128985876</v>
       </c>
       <c r="B15" t="n">
-        <v>86980</v>
+        <v>92505</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720504</v>
+        <v>720766</v>
       </c>
       <c r="R15" t="n">
-        <v>6626377</v>
+        <v>6626378</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985879</v>
+        <v>128985908</v>
       </c>
       <c r="B16" t="n">
-        <v>92867</v>
+        <v>86981</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2065,37 +2065,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720754</v>
+        <v>720504</v>
       </c>
       <c r="R16" t="n">
-        <v>6626384</v>
+        <v>6626377</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2136,7 +2133,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2155,10 +2151,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985876</v>
+        <v>128985879</v>
       </c>
       <c r="B17" t="n">
-        <v>92504</v>
+        <v>92868</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2166,34 +2162,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720766</v>
+        <v>720754</v>
       </c>
       <c r="R17" t="n">
-        <v>6626378</v>
+        <v>6626384</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2234,6 +2233,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985895</v>
+        <v>128985885</v>
       </c>
       <c r="B18" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720572</v>
+        <v>720573</v>
       </c>
       <c r="R18" t="n">
-        <v>6626395</v>
+        <v>6626380</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985885</v>
+        <v>128985895</v>
       </c>
       <c r="B19" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720573</v>
+        <v>720572</v>
       </c>
       <c r="R19" t="n">
-        <v>6626380</v>
+        <v>6626395</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2454,48 +2454,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985896</v>
+        <v>128985873</v>
       </c>
       <c r="B20" t="n">
-        <v>92867</v>
+        <v>86897</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>445</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720577</v>
+        <v>720771</v>
       </c>
       <c r="R20" t="n">
-        <v>6626370</v>
+        <v>6626378</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2536,7 +2533,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2555,10 +2551,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B21" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,10 +2589,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R21" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2656,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985899</v>
+        <v>128985875</v>
       </c>
       <c r="B22" t="n">
-        <v>58584</v>
+        <v>92868</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2667,34 +2663,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208250</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720542</v>
+        <v>720769</v>
       </c>
       <c r="R22" t="n">
-        <v>6626391</v>
+        <v>6626395</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2735,6 +2734,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2753,48 +2753,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985882</v>
+        <v>128985899</v>
       </c>
       <c r="B23" t="n">
-        <v>91931</v>
+        <v>58584</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1506</v>
+        <v>208250</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720643</v>
+        <v>720542</v>
       </c>
       <c r="R23" t="n">
-        <v>6626413</v>
+        <v>6626391</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2829,11 +2826,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2842,26 +2834,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2878,10 +2850,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985873</v>
+        <v>128985882</v>
       </c>
       <c r="B24" t="n">
-        <v>86896</v>
+        <v>91932</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2889,34 +2861,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>445</v>
+        <v>1506</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720771</v>
+        <v>720643</v>
       </c>
       <c r="R24" t="n">
-        <v>6626378</v>
+        <v>6626413</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2951,6 +2926,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -2959,6 +2939,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -2978,7 +2978,7 @@
         <v>128985902</v>
       </c>
       <c r="B25" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -781,45 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128985878</v>
+        <v>128985894</v>
       </c>
       <c r="B3" t="n">
-        <v>92850</v>
+        <v>92868</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720769</v>
+        <v>720563</v>
       </c>
       <c r="R3" t="n">
-        <v>6626378</v>
+        <v>6626412</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,6 +863,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -878,48 +882,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128985894</v>
+        <v>128985878</v>
       </c>
       <c r="B4" t="n">
-        <v>92868</v>
+        <v>92850</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720563</v>
+        <v>720769</v>
       </c>
       <c r="R4" t="n">
-        <v>6626412</v>
+        <v>6626378</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -960,7 +961,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128985884</v>
+        <v>128985897</v>
       </c>
       <c r="B5" t="n">
-        <v>98746</v>
+        <v>92868</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,34 +990,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720568</v>
+        <v>720543</v>
       </c>
       <c r="R5" t="n">
-        <v>6626387</v>
+        <v>6626360</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1058,6 +1061,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1076,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985897</v>
+        <v>128985884</v>
       </c>
       <c r="B6" t="n">
-        <v>92868</v>
+        <v>98746</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,37 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720543</v>
+        <v>720568</v>
       </c>
       <c r="R6" t="n">
-        <v>6626360</v>
+        <v>6626387</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1158,7 +1159,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985876</v>
+        <v>128985908</v>
       </c>
       <c r="B15" t="n">
-        <v>92505</v>
+        <v>86981</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>1988</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720766</v>
+        <v>720504</v>
       </c>
       <c r="R15" t="n">
-        <v>6626378</v>
+        <v>6626377</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985908</v>
+        <v>128985879</v>
       </c>
       <c r="B16" t="n">
-        <v>86981</v>
+        <v>92868</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2065,34 +2065,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1988</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720504</v>
+        <v>720754</v>
       </c>
       <c r="R16" t="n">
-        <v>6626377</v>
+        <v>6626384</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2133,6 +2136,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2151,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985879</v>
+        <v>128985876</v>
       </c>
       <c r="B17" t="n">
-        <v>92868</v>
+        <v>92505</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2162,37 +2166,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720754</v>
+        <v>720766</v>
       </c>
       <c r="R17" t="n">
-        <v>6626384</v>
+        <v>6626378</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2233,7 +2234,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2551,32 +2551,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985896</v>
+        <v>128985882</v>
       </c>
       <c r="B21" t="n">
-        <v>92868</v>
+        <v>91932</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>1506</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720577</v>
+        <v>720643</v>
       </c>
       <c r="R21" t="n">
-        <v>6626370</v>
+        <v>6626413</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2627,15 +2627,39 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2652,7 +2676,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985875</v>
+        <v>128985896</v>
       </c>
       <c r="B22" t="n">
         <v>92868</v>
@@ -2690,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720769</v>
+        <v>720577</v>
       </c>
       <c r="R22" t="n">
-        <v>6626395</v>
+        <v>6626370</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2753,10 +2777,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985899</v>
+        <v>128985875</v>
       </c>
       <c r="B23" t="n">
-        <v>58584</v>
+        <v>92868</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2764,34 +2788,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>208250</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720542</v>
+        <v>720769</v>
       </c>
       <c r="R23" t="n">
-        <v>6626391</v>
+        <v>6626395</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2832,6 +2859,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2850,48 +2878,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128985882</v>
+        <v>128985902</v>
       </c>
       <c r="B24" t="n">
-        <v>91932</v>
+        <v>92505</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1506</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720643</v>
+        <v>720521</v>
       </c>
       <c r="R24" t="n">
-        <v>6626413</v>
+        <v>6626387</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2926,11 +2951,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -2939,26 +2959,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -2975,10 +2975,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985902</v>
+        <v>128985899</v>
       </c>
       <c r="B25" t="n">
-        <v>92505</v>
+        <v>58584</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2986,21 +2986,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4769</v>
+        <v>208250</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720521</v>
+        <v>720542</v>
       </c>
       <c r="R25" t="n">
-        <v>6626387</v>
+        <v>6626391</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -2252,7 +2252,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985885</v>
+        <v>128985895</v>
       </c>
       <c r="B18" t="n">
         <v>92868</v>
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720573</v>
+        <v>720572</v>
       </c>
       <c r="R18" t="n">
-        <v>6626380</v>
+        <v>6626395</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2353,7 +2353,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985895</v>
+        <v>128985885</v>
       </c>
       <c r="B19" t="n">
         <v>92868</v>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720572</v>
+        <v>720573</v>
       </c>
       <c r="R19" t="n">
-        <v>6626395</v>
+        <v>6626380</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2454,45 +2454,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985873</v>
+        <v>128985896</v>
       </c>
       <c r="B20" t="n">
-        <v>86897</v>
+        <v>92868</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720771</v>
+        <v>720577</v>
       </c>
       <c r="R20" t="n">
-        <v>6626378</v>
+        <v>6626370</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2533,6 +2536,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2551,32 +2555,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985882</v>
+        <v>128985875</v>
       </c>
       <c r="B21" t="n">
-        <v>91932</v>
+        <v>92868</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1506</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2589,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720643</v>
+        <v>720769</v>
       </c>
       <c r="R21" t="n">
-        <v>6626413</v>
+        <v>6626395</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2627,39 +2631,15 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2676,48 +2656,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985896</v>
+        <v>128985873</v>
       </c>
       <c r="B22" t="n">
-        <v>92868</v>
+        <v>86897</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>445</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720577</v>
+        <v>720771</v>
       </c>
       <c r="R22" t="n">
-        <v>6626370</v>
+        <v>6626378</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2758,7 +2735,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2777,32 +2753,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985875</v>
+        <v>128985882</v>
       </c>
       <c r="B23" t="n">
-        <v>92868</v>
+        <v>91932</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>1506</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2815,10 +2791,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720769</v>
+        <v>720643</v>
       </c>
       <c r="R23" t="n">
-        <v>6626395</v>
+        <v>6626413</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2853,15 +2829,39 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124665953</v>
+        <v>128985906</v>
       </c>
       <c r="B2" t="n">
-        <v>98291</v>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bollen, Upl</t>
+          <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720564</v>
+        <v>720486</v>
       </c>
       <c r="R2" t="n">
-        <v>6626375</v>
+        <v>6626330</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktor Lund, Joakim Ekman</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128985894</v>
+        <v>124663398</v>
       </c>
       <c r="B3" t="n">
-        <v>92868</v>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,40 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rådmansö, Upl</t>
+          <t>Pilkrogsudden, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720563</v>
+        <v>720795</v>
       </c>
       <c r="R3" t="n">
-        <v>6626412</v>
+        <v>6626271</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,29 +851,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Viktor Lund, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128985878</v>
+        <v>131431262</v>
       </c>
       <c r="B4" t="n">
-        <v>92850</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rådmansö, Upl</t>
+          <t>Bollen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720769</v>
+        <v>720598</v>
       </c>
       <c r="R4" t="n">
-        <v>6626378</v>
+        <v>6626321</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -967,60 +954,61 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Karina Hälleberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128985897</v>
+        <v>128985904</v>
       </c>
       <c r="B5" t="n">
-        <v>92868</v>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720543</v>
+        <v>720496</v>
       </c>
       <c r="R5" t="n">
-        <v>6626360</v>
+        <v>6626331</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1061,7 +1049,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1080,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128985884</v>
+        <v>128985862</v>
       </c>
       <c r="B6" t="n">
-        <v>98746</v>
+        <v>91409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>5741</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1115,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720568</v>
+        <v>720770</v>
       </c>
       <c r="R6" t="n">
-        <v>6626387</v>
+        <v>6626291</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1177,45 +1164,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128985900</v>
+        <v>128985863</v>
       </c>
       <c r="B7" t="n">
-        <v>92505</v>
+        <v>93233</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720544</v>
+        <v>720755</v>
       </c>
       <c r="R7" t="n">
-        <v>6626397</v>
+        <v>6626301</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1256,6 +1246,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1274,45 +1265,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128985886</v>
+        <v>128985865</v>
       </c>
       <c r="B8" t="n">
-        <v>92505</v>
+        <v>93233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720581</v>
+        <v>720780</v>
       </c>
       <c r="R8" t="n">
-        <v>6626397</v>
+        <v>6626277</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1353,6 +1347,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1371,14 +1366,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128985888</v>
+        <v>128985897</v>
       </c>
       <c r="B9" t="n">
-        <v>92868</v>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1409,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720578</v>
+        <v>720543</v>
       </c>
       <c r="R9" t="n">
-        <v>6626426</v>
+        <v>6626360</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1472,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128985887</v>
+        <v>131431264</v>
       </c>
       <c r="B10" t="n">
-        <v>105777</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1483,37 +1478,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224098</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rådmansö, Upl</t>
+          <t>Bollen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720586</v>
+        <v>720729</v>
       </c>
       <c r="R10" t="n">
-        <v>6626407</v>
+        <v>6626290</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1537,12 +1532,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1557,22 +1552,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Karina Hälleberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128985901</v>
+        <v>128985907</v>
       </c>
       <c r="B11" t="n">
-        <v>92505</v>
+        <v>101325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1580,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1604,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720521</v>
+        <v>720516</v>
       </c>
       <c r="R11" t="n">
-        <v>6626398</v>
+        <v>6626359</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1666,48 +1665,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128985898</v>
+        <v>132011507</v>
       </c>
       <c r="B12" t="n">
-        <v>91323</v>
+        <v>91993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3215</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Rödgul trumpetsvamp</t>
-        </is>
+        <v>6332881</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rådmansö, Upl</t>
+          <t>Bollen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720530</v>
+        <v>720505</v>
       </c>
       <c r="R12" t="n">
-        <v>6626369</v>
+        <v>6626362</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1731,12 +1725,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1751,44 +1745,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128985907</v>
+        <v>128985883</v>
       </c>
       <c r="B13" t="n">
-        <v>100913</v>
+        <v>89799</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>37</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1798,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720516</v>
+        <v>720621</v>
       </c>
       <c r="R13" t="n">
-        <v>6626359</v>
+        <v>6626429</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1834,6 +1828,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Under björk, gran och hassel i vildsvinsbök.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1860,32 +1859,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128985893</v>
+        <v>128985873</v>
       </c>
       <c r="B14" t="n">
-        <v>58586</v>
+        <v>87238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208249</v>
+        <v>445</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1895,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720574</v>
+        <v>720771</v>
       </c>
       <c r="R14" t="n">
-        <v>6626394</v>
+        <v>6626378</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1957,45 +1956,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128985908</v>
+        <v>128985882</v>
       </c>
       <c r="B15" t="n">
-        <v>86981</v>
+        <v>92292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1988</v>
+        <v>1506</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720504</v>
+        <v>720643</v>
       </c>
       <c r="R15" t="n">
-        <v>6626377</v>
+        <v>6626413</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2030,6 +2032,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2038,6 +2045,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2054,48 +2081,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128985879</v>
+        <v>128985908</v>
       </c>
       <c r="B16" t="n">
-        <v>92868</v>
+        <v>87322</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720754</v>
+        <v>720504</v>
       </c>
       <c r="R16" t="n">
-        <v>6626384</v>
+        <v>6626377</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2136,7 +2160,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2155,10 +2178,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128985876</v>
+        <v>128985898</v>
       </c>
       <c r="B17" t="n">
-        <v>92505</v>
+        <v>91680</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2166,21 +2189,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2213,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720766</v>
+        <v>720530</v>
       </c>
       <c r="R17" t="n">
-        <v>6626378</v>
+        <v>6626369</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2252,48 +2275,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128985895</v>
+        <v>128985890</v>
       </c>
       <c r="B18" t="n">
-        <v>92868</v>
+        <v>87247</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720572</v>
+        <v>720530</v>
       </c>
       <c r="R18" t="n">
-        <v>6626395</v>
+        <v>6626415</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2334,7 +2354,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2353,48 +2372,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128985885</v>
+        <v>128985878</v>
       </c>
       <c r="B19" t="n">
-        <v>92868</v>
+        <v>93215</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720573</v>
+        <v>720769</v>
       </c>
       <c r="R19" t="n">
-        <v>6626380</v>
+        <v>6626378</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2435,7 +2451,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2454,10 +2469,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128985896</v>
+        <v>128985876</v>
       </c>
       <c r="B20" t="n">
-        <v>92868</v>
+        <v>92869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2465,37 +2480,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720577</v>
+        <v>720766</v>
       </c>
       <c r="R20" t="n">
-        <v>6626370</v>
+        <v>6626378</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2536,7 +2548,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2555,10 +2566,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128985875</v>
+        <v>128985886</v>
       </c>
       <c r="B21" t="n">
-        <v>92868</v>
+        <v>92869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2566,37 +2577,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720769</v>
+        <v>720581</v>
       </c>
       <c r="R21" t="n">
-        <v>6626395</v>
+        <v>6626397</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2637,7 +2645,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2656,32 +2663,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128985873</v>
+        <v>128985900</v>
       </c>
       <c r="B22" t="n">
-        <v>86897</v>
+        <v>92869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>445</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2691,10 +2698,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720771</v>
+        <v>720544</v>
       </c>
       <c r="R22" t="n">
-        <v>6626378</v>
+        <v>6626397</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2753,48 +2760,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128985882</v>
+        <v>128985901</v>
       </c>
       <c r="B23" t="n">
-        <v>91932</v>
+        <v>92869</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1506</v>
+        <v>4769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720643</v>
+        <v>720521</v>
       </c>
       <c r="R23" t="n">
-        <v>6626413</v>
+        <v>6626398</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2829,11 +2833,6 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar på grov, avsågad granlåga.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2842,26 +2841,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2881,7 +2860,7 @@
         <v>128985902</v>
       </c>
       <c r="B24" t="n">
-        <v>92505</v>
+        <v>92869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2975,45 +2954,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128985899</v>
+        <v>128985875</v>
       </c>
       <c r="B25" t="n">
-        <v>58584</v>
+        <v>93233</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208250</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rådmansö, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720542</v>
+        <v>720769</v>
       </c>
       <c r="R25" t="n">
-        <v>6626391</v>
+        <v>6626395</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3054,6 +3036,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3069,6 +3052,1419 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128985879</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>720754</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6626384</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128985885</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>720573</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6626380</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128985888</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>720578</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6626426</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128985889</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>720564</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6626459</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128985894</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>720563</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6626412</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128985895</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>720572</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6626395</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128985896</v>
+      </c>
+      <c r="B32" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>720577</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6626370</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128985891</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>720531</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6626414</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128985893</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>720574</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6626394</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128985899</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>720542</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6626391</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124665953</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bollen, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>720564</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6626375</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128985884</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>720568</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6626387</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>124664322</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Holmängsviken, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>720870</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6626379</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128985887</v>
+      </c>
+      <c r="B39" t="n">
+        <v>106230</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Rådmansö, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>720586</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6626407</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985883</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985906</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985873</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124663398</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985882</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985908</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985898</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985890</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,6 +1627,11 @@
           <t>Värdefull natur i Stockholms län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131431262</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1679,6 +1729,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985904</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1776,6 +1831,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985878</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1873,6 +1933,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985876</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1970,6 +2035,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985886</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2067,6 +2137,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985900</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2164,6 +2239,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985901</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2261,6 +2341,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985902</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2358,6 +2443,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985862</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2459,6 +2549,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985863</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2560,6 +2655,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985865</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2661,6 +2761,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985875</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2762,6 +2867,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985879</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2863,6 +2973,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985885</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2964,6 +3079,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985888</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3065,6 +3185,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985889</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3166,6 +3291,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985894</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3267,6 +3397,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985895</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3368,6 +3503,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985896</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3469,6 +3609,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985897</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3584,6 +3729,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985891</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3685,6 +3835,11 @@
           <t>Värdefull natur i Stockholms län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131431264</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3782,6 +3937,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985893</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3879,6 +4039,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985899</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3985,6 +4150,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124665953</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4082,6 +4252,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985884</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4179,6 +4354,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124664322</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4276,6 +4456,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985907</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4373,6 +4558,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128985887</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4465,8 +4655,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132011507</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -1740,7 +1740,7 @@
         <v>128985878</v>
       </c>
       <c r="B12" t="n">
-        <v>93215</v>
+        <v>93365</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -1740,7 +1740,7 @@
         <v>128985878</v>
       </c>
       <c r="B12" t="n">
-        <v>93365</v>
+        <v>93380</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -1740,7 +1740,7 @@
         <v>128985878</v>
       </c>
       <c r="B12" t="n">
-        <v>93380</v>
+        <v>93381</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -1740,7 +1740,7 @@
         <v>128985878</v>
       </c>
       <c r="B12" t="n">
-        <v>93381</v>
+        <v>93382</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -1740,7 +1740,7 @@
         <v>128985878</v>
       </c>
       <c r="B12" t="n">
-        <v>93382</v>
+        <v>93383</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -1740,7 +1740,7 @@
         <v>128985878</v>
       </c>
       <c r="B12" t="n">
-        <v>93383</v>
+        <v>93389</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -1740,7 +1740,7 @@
         <v>128985878</v>
       </c>
       <c r="B12" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -1740,7 +1740,7 @@
         <v>128985878</v>
       </c>
       <c r="B12" t="n">
-        <v>93390</v>
+        <v>93396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -1740,7 +1740,7 @@
         <v>128985878</v>
       </c>
       <c r="B12" t="n">
-        <v>93396</v>
+        <v>93403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -1740,7 +1740,7 @@
         <v>128985878</v>
       </c>
       <c r="B12" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -1740,7 +1740,7 @@
         <v>128985878</v>
       </c>
       <c r="B12" t="n">
-        <v>93404</v>
+        <v>93417</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 21927-2025 artfynd.xlsx
+++ b/artfynd/A 21927-2025 artfynd.xlsx
@@ -1740,7 +1740,7 @@
         <v>128985878</v>
       </c>
       <c r="B12" t="n">
-        <v>93417</v>
+        <v>93418</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
